--- a/Federal/f1040sse-2025.xlsx
+++ b/Federal/f1040sse-2025.xlsx
@@ -169,7 +169,7 @@
     <t xml:space="preserve">13</t>
   </si>
   <si>
-    <t xml:space="preserve">Deduction for one-half of self-employment tax.  Multiply line 12 by 50% (0.50). Enter here and on Schedule 1 (Form 1040), line 14</t>
+    <t xml:space="preserve">Deduction for one-half of self-employment tax.  Multiply line 12 by 50% (0.50). Enter here and on Schedule 1 (Form 1040), line 15</t>
   </si>
   <si>
     <t xml:space="preserve">Part II  Optional Methods To Figure Net Earnings (see instructions)</t>
@@ -687,7 +687,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G44"/>
-  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="78.58"/>
